--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}nemsms-invariant:If communication resource is a NemSMS payload cannot exceed 160 {medium.coding.where(code = 'nemsms').exists() implies payload.content.ofType(string).length() &lt;= 160}note-invariant:Category note invariant {category.coding.code contains 'note' implies (recipient.reference contains sender.reference) or (recipient.reference.exists().not() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists())}notification-invariant:Category notification invariant {category.coding.code contains 'notification' implies (recipient.reference.contains('Patient/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}message-invariant:Category message invariant {category.coding.code contains 'message' implies (recipient.reference.contains('Patient/') and ( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists())) or (( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and (sender.reference.contains('Patient/')) or (extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists() ))}advice-invariant:Category advice invariant {category.coding.code contains 'advice' implies (recipient.reference.contains('Patient/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}nemsms-invariant:If communication resource is a NemSMS payload cannot exceed 160 {medium.coding.where(code = 'nemsms').exists() implies payload.content.ofType(string).length() &lt;= 160}note-invariant:Category note invariant {category.coding.code contains 'note' implies (recipient.reference contains sender.reference) or (recipient.reference.exists().not() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists())}notification-invariant:Category notification invariant {category.coding.code contains 'notification' implies (recipient.reference.contains('Patient/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}message-invariant:Category message invariant {category.coding.code contains 'message' implies (recipient.reference.contains('Patient/') and ( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists())) or (( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and (sender.reference.contains('Patient/')) or (extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists() ))}advice-invariant:Category advice invariant {category.coding.code contains 'advice' implies (recipient.reference.contains('Patient/') or recipient.reference.contains('RelatedPerson/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -355,7 +355,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -755,7 +755,7 @@
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -793,7 +793,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
     <t>Communication.inResponseTo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Communication)
+    <t xml:space="preserve">Reference(Communication|4.0.1)
 </t>
   </si>
   <si>
@@ -895,7 +895,7 @@
     <t>Codes for the reason why a communication did not happen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -916,7 +916,7 @@
     <t>Codes for general categories of communications such as alerts, instructions, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-category</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1259,7 +1259,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1290,7 +1290,7 @@
     <t>Codes describing the purpose or content of the communication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/communication-topic|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.context</t>
@@ -1311,7 +1311,7 @@
     <t>Communication.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1361,7 +1361,7 @@
     <t>Communication.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner) &lt;&lt;referenced&gt;&gt;
+    <t xml:space="preserve">Reference(Patient|Practitioner|http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-relatedperson) &lt;&lt;referenced&gt;&gt;
 </t>
   </si>
   <si>
@@ -1516,7 +1516,7 @@
     <t>Communication.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1923,7 +1923,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.65234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4485,7 +4485,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>210</v>
       </c>
@@ -11343,12 +11343,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM85">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}nemsms-invariant:If communication resource is a NemSMS payload cannot exceed 160 {medium.coding.where(code = 'nemsms').exists() implies payload.content.ofType(string).length() &lt;= 160}note-invariant:Category note invariant {category.coding.code contains 'note' implies (recipient.reference contains sender.reference) or (recipient.reference.exists().not() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists())}notification-invariant:Category notification invariant {category.coding.code contains 'notification' implies (recipient.reference.contains('Patient/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}message-invariant:Category message invariant {category.coding.code contains 'message' implies (recipient.reference.contains('Patient/') and ( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists())) or (( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and (sender.reference.contains('Patient/')) or (extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists() ))}advice-invariant:Category advice invariant {category.coding.code contains 'advice' implies (recipient.reference.contains('Patient/') or recipient.reference.contains('RelatedPerson/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}nemsms-invariant:If communication resource is a NemSMS payload cannot exceed 160 {medium.coding.where(code = 'nemsms').exists() implies payload.content.ofType(string).length() &lt;= 160}note-invariant:Category note invariant {category.coding.code contains 'note' implies (recipient.reference contains sender.reference) or (recipient.reference.exists().not() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists())}notification-invariant:Category notification invariant {category.coding.code contains 'notification' implies (recipient.reference.contains('Patient/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}message-invariant:Category message invariant {category.coding.code contains 'message' implies (recipient.reference.contains('Patient/') and ( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists())) or (( extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and (sender.reference.contains('Patient/')) or (extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists() and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-senderCareTeam').value.as(Reference).exists() )) or (sender.reference.contains('RelatedPerson/') and extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-on-behalf-of').value.as(Reference).reference.contains('Patient/'))}advice-invariant:Category advice invariant {category.coding.code contains 'advice' implies (recipient.reference.contains('Patient/') or recipient.reference.contains('RelatedPerson/') or extension.where(url = 'http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-communication-recipientCareTeam').value.as(Reference).exists()) and ( sender.reference.contains('Device/') or contained.ofType(Device).where('#' + id = %resource.sender.reference).empty().not())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1380,7 +1380,7 @@
     <t>Communication.sender</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Patient|Practitioner) &lt;&lt;referenced, contained&gt;&gt;
+    <t xml:space="preserve">Reference(Device|Patient|Practitioner|RelatedPerson) &lt;&lt;referenced, contained&gt;&gt;
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-message.xlsx
+++ b/fhir/StructureDefinition-ehealth-message.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
